--- a/app-templates/users (21).xlsx
+++ b/app-templates/users (21).xlsx
@@ -226,7 +226,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -248,12 +248,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,7 +588,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -618,16 +612,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -636,85 +630,85 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -737,14 +731,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1517,7 +1511,7 @@
       <c r="AI6" s="5"/>
     </row>
     <row r="7" spans="2:35">
-      <c r="B7" s="5"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1553,43 +1547,43 @@
       <c r="AI7" s="5"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="2:35">
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
-      <c r="AE8" s="7"/>
-      <c r="AF8" s="7"/>
-      <c r="AG8" s="7"/>
-      <c r="AH8" s="7"/>
-      <c r="AI8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
     </row>
     <row r="9" spans="2:35">
-      <c r="B9" s="8"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>

--- a/app-templates/users (21).xlsx
+++ b/app-templates/users (21).xlsx
@@ -11,10 +11,11 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="NgayLabel">Export!$C$4</definedName>
+    <definedName name="NgayLabel">Export!$F$4</definedName>
     <definedName name="ngayValue">Export!$F$4</definedName>
-    <definedName name="header">Export!$C$8:$AI$8</definedName>
-    <definedName name="value">Export!$C$9:$AI$9</definedName>
+    <definedName name="han">Export!$C$9</definedName>
+    <definedName name="ten">Export!$K$9</definedName>
+    <definedName name="so">Export!$P$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
